--- a/data/trans_camb/IP1002-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,85</t>
+          <t>-2,6; 1,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,27</t>
+          <t>-3,17; 1,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,86</t>
+          <t>-1,4; 4,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,5</t>
+          <t>0,63; 6,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,91</t>
+          <t>-1,01; 1,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,49</t>
+          <t>-0,7; 2,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,28</t>
+          <t>-0,78; 2,26</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,64</t>
+          <t>-4,54; 0,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 0,0</t>
+          <t>-5,54; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,44</t>
+          <t>-4,67; 0,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 3,63</t>
+          <t>-3,53; 3,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,87</t>
+          <t>-4,61; 1,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 7,45</t>
+          <t>-2,01; 7,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,57</t>
+          <t>-2,37; 1,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,53</t>
+          <t>-2,94; 0,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,43</t>
+          <t>-1,99; 3,31</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 349,23</t>
+          <t>-88,22; 500,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-89,19; 718,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,53</t>
+          <t>-3,04; 3,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,0</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,0</t>
+          <t>-4,42; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,74</t>
+          <t>-1,4; 3,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,92</t>
+          <t>-1,43; 2,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 10,64</t>
+          <t>-1,41; 9,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,8</t>
+          <t>-1,21; 2,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,96</t>
+          <t>-1,68; 0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,18</t>
+          <t>-1,25; 4,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,33</t>
+          <t>-0,76; 3,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,79</t>
+          <t>-0,95; 2,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,36</t>
+          <t>-1,59; 2,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,31</t>
+          <t>-0,52; 5,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,86</t>
+          <t>-3,02; 1,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,34</t>
+          <t>-3,07; 1,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 3,66</t>
+          <t>0,12; 3,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,39</t>
+          <t>-1,46; 1,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,16</t>
+          <t>-1,6; 1,2</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,7; 692,23</t>
+          <t>-58,07; 806,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 641,15</t>
+          <t>-64,38; 855,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-85,07; 727,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 605,53</t>
+          <t>-25,96; 561,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,72; 153,81</t>
+          <t>-89,51; 162,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 262,74</t>
+          <t>-100,0; 229,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 378,64</t>
+          <t>0,2; 382,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-55,93; 148,46</t>
+          <t>-62,53; 152,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,14; 133,72</t>
+          <t>-72,08; 164,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,82</t>
+          <t>-3,73; 2,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 1,85</t>
+          <t>-4,32; 1,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,23</t>
+          <t>-3,96; 2,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,03</t>
+          <t>-1,23; 2,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,88</t>
+          <t>-0,77; 3,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,3</t>
+          <t>-1,25; 2,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,1</t>
+          <t>-1,66; 1,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,77</t>
+          <t>-1,83; 1,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,68</t>
+          <t>-1,84; 1,7</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,11; 376,52</t>
+          <t>-83,9; 417,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 395,76</t>
+          <t>-73,28; 319,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-76,83; 338,91</t>
+          <t>-82,13; 310,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-77,84; 282,42</t>
+          <t>-79,43; 318,52</t>
         </is>
       </c>
     </row>
@@ -1762,42 +1762,42 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,64</t>
+          <t>-2,16; 4,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,93</t>
+          <t>-3,06; 1,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,56</t>
+          <t>-2,01; 3,8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,61</t>
+          <t>-0,98; 3,01</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,32</t>
+          <t>-0,99; 2,28</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,52</t>
+          <t>-0,98; 2,53</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,33</t>
+          <t>-0,75; 1,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,78</t>
+          <t>-1,15; 0,86</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,02</t>
+          <t>-1,04; 1,07</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,36</t>
+          <t>0,05; 2,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,12</t>
+          <t>-0,76; 1,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,49</t>
+          <t>-0,68; 1,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,58</t>
+          <t>-0,02; 1,61</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,71</t>
+          <t>-0,67; 0,76</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,93</t>
+          <t>-0,62; 0,98</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 151,81</t>
+          <t>-44,14; 173,01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-64,2; 101,93</t>
+          <t>-64,24; 118,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 129,25</t>
+          <t>-56,96; 132,11</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 367,32</t>
+          <t>-3,33; 352,33</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,12; 174,23</t>
+          <t>-50,64; 168,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 237,49</t>
+          <t>-48,81; 225,49</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 173,22</t>
+          <t>-3,55; 189,76</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,11; 81,08</t>
+          <t>-42,09; 91,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 97,78</t>
+          <t>-37,97; 107,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,84</t>
+          <t>-2,62; 1,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,32</t>
+          <t>-3,21; 1,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,78</t>
+          <t>-1,37; 4,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,08</t>
+          <t>0,64; 5,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,66</t>
+          <t>-1,22; 1,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,57</t>
+          <t>-0,71; 2,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,26</t>
+          <t>-0,73; 2,29</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,62</t>
+          <t>-3,92; 0,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,0</t>
+          <t>-4,69; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,45</t>
+          <t>-4,22; 0,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,64</t>
+          <t>-3,53; 4,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 1,68</t>
+          <t>-4,49; 1,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 7,28</t>
+          <t>-2,24; 8,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,82</t>
+          <t>-2,6; 1,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,73</t>
+          <t>-3,33; 0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,31</t>
+          <t>-2,03; 3,53</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,22; 500,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,09</t>
+          <t>-2,33; 3,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-5,12; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 0,0</t>
+          <t>-4,99; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,86</t>
+          <t>-1,4; 3,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,81</t>
+          <t>-1,42; 2,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 9,36</t>
+          <t>-1,4; 11,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,71</t>
+          <t>-1,29; 2,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,98</t>
+          <t>-2,0; 0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,91</t>
+          <t>-1,24; 7,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,49</t>
+          <t>-0,78; 3,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,89</t>
+          <t>-1,05; 2,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,23</t>
+          <t>-1,53; 2,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,24</t>
+          <t>-0,48; 5,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,01</t>
+          <t>-2,96; 1,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,2</t>
+          <t>-2,78; 1,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,51</t>
+          <t>-0,06; 3,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,3</t>
+          <t>-1,3; 1,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,2</t>
+          <t>-1,7; 1,09</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,07; 806,83</t>
+          <t>-60,53; 867,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,38; 855,08</t>
+          <t>-68,53; 720,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,68; 695,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 561,5</t>
+          <t>-28,44; 510,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,51; 162,61</t>
+          <t>-87,4; 224,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 229,45</t>
+          <t>-100,0; 227,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 382,87</t>
+          <t>-9,4; 364,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,53; 152,09</t>
+          <t>-58,52; 149,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 164,89</t>
+          <t>-73,15; 131,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,91</t>
+          <t>-3,45; 2,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,9</t>
+          <t>-4,05; 1,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,7</t>
+          <t>-3,98; 2,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,02</t>
+          <t>-1,2; 2,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,15</t>
+          <t>-0,8; 3,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,16</t>
+          <t>-1,13; 2,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,83</t>
+          <t>-1,75; 1,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,76</t>
+          <t>-1,66; 1,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,7</t>
+          <t>-1,75; 1,6</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-83,9; 417,45</t>
+          <t>-86,12; 446,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 421,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-73,28; 319,92</t>
+          <t>-70,15; 313,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-82,13; 310,31</t>
+          <t>-81,49; 270,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-79,43; 318,52</t>
+          <t>-79,75; 315,59</t>
         </is>
       </c>
     </row>
@@ -1762,42 +1762,42 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 4,28</t>
+          <t>-2,96; 3,64</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,97</t>
+          <t>-3,03; 1,95</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,8</t>
+          <t>-2,01; 3,84</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,01</t>
+          <t>-0,98; 3,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,28</t>
+          <t>-0,99; 2,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,53</t>
+          <t>-0,99; 2,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,41</t>
+          <t>-0,85; 1,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,86</t>
+          <t>-1,16; 0,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,07</t>
+          <t>-1,06; 1,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,45</t>
+          <t>0,15; 2,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,1</t>
+          <t>-0,78; 1,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,43</t>
+          <t>-0,67; 1,51</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,61</t>
+          <t>-0,09; 1,54</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,76</t>
+          <t>-0,69; 0,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,98</t>
+          <t>-0,58; 0,94</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,14; 173,01</t>
+          <t>-45,8; 162,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-64,24; 118,62</t>
+          <t>-65,33; 95,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-56,96; 132,11</t>
+          <t>-61,85; 120,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 352,33</t>
+          <t>2,73; 356,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 168,72</t>
+          <t>-50,4; 164,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 225,49</t>
+          <t>-48,6; 224,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 189,76</t>
+          <t>-6,93; 162,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-42,09; 91,52</t>
+          <t>-44,59; 71,91</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 107,95</t>
+          <t>-37,75; 101,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,02</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,63</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,71</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,61</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,29</t>
+          <t>0,63; 5,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,82</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>-2,73; 1,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,43</t>
+          <t>-3,17; 1,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>-1,29; 5,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,62</t>
+          <t>-0,98; 1,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,54</t>
+          <t>-0,69; 2,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,29</t>
+          <t>-0,57; 2,56</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-40,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-49,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104,03%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>111,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>107,12%</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,99</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,52</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 0,62</t>
+          <t>-3,1; 3,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,0</t>
+          <t>-4,51; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,56</t>
+          <t>-1,82; 8,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 4,03</t>
+          <t>-4,44; 0,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 1,9</t>
+          <t>-4,49; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 8,42</t>
+          <t>-4,97; 0,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,75</t>
+          <t>-2,46; 1,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,51</t>
+          <t>-3,02; 0,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,53</t>
+          <t>-1,94; 3,45</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26,21%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-30,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>113,18%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-59,7%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-70,69%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-30,2%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>102,49%</t>
+          <t>-75,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 349,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,54; 903,68</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,81</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,05</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,55</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,71</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,8</t>
+          <t>-1,43; 3,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,0</t>
+          <t>-1,42; 2,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,0</t>
+          <t>-1,41; 7,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,82</t>
+          <t>-2,24; 3,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,98</t>
+          <t>-6,08; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 11,44</t>
+          <t>-5,01; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,59</t>
+          <t>-1,21; 2,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,98</t>
+          <t>-2,06; 0,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 7,03</t>
+          <t>-1,61; 2,91</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>115,12%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149,36%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>55,02%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>115,12%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>245,76%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>86,01%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,78</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,09</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,82</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,28</t>
+          <t>-0,4; 5,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,81</t>
+          <t>-3,09; 0,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,11</t>
+          <t>-2,81; 1,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,09</t>
+          <t>-0,92; 3,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,17</t>
+          <t>-0,99; 2,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,37</t>
+          <t>-1,16; 3,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,55</t>
+          <t>-0,19; 3,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,34</t>
+          <t>-1,32; 1,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,09</t>
+          <t>-1,6; 1,63</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>107,29%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-42,58%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-37,99%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>91,43%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>69,0%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17,84%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>107,29%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-42,58%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-41,98%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,19%</t>
+          <t>-7,11%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,53; 867,02</t>
+          <t>-22,35; 605,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 720,72</t>
+          <t>-89,72; 153,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-87,68; 695,32</t>
+          <t>-100,0; 287,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 510,01</t>
+          <t>-64,7; 692,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,4; 224,75</t>
+          <t>-71,45; 641,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,39</t>
+          <t>-78,95; 977,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 364,69</t>
+          <t>-10,79; 378,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,52; 149,48</t>
+          <t>-55,93; 148,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,15; 131,62</t>
+          <t>-67,4; 173,44</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,92</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,56</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,96</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>-0,86</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-0,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,92</t>
+          <t>-1,2; 2,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,92</t>
+          <t>-1,12; 2,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,53</t>
+          <t>-1,14; 2,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,41</t>
+          <t>-3,64; 2,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,09</t>
+          <t>-4,6; 1,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,47</t>
+          <t>-4,62; 2,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,89</t>
+          <t>-1,46; 2,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,73</t>
+          <t>-1,69; 1,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,6</t>
+          <t>-1,87; 1,68</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>70,99%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>161,58%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-5,5%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-38,16%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-29,86%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>161,58%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>-34,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-3,61%</t>
+          <t>-5,89%</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-86,12; 446,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 421,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,11; 376,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-70,15; 313,12</t>
+          <t>-72,39; 395,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-81,49; 270,48</t>
+          <t>-76,83; 338,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-79,75; 315,59</t>
+          <t>-78,75; 302,91</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,79</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>0,92</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,19; 3,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>-4,01; 1,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>-2,01; 5,26</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 3,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,95</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,84</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,16</t>
+          <t>-0,95; 2,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,35</t>
+          <t>-0,99; 2,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,29</t>
+          <t>-0,98; 2,59</t>
         </is>
       </c>
     </row>
@@ -1810,34 +1810,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>78,42%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-4,57%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>78,42%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-4,57%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>110,02%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,18</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,29</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-0,16</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,35</t>
+          <t>0,03; 2,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,81</t>
+          <t>-0,8; 1,12</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,01</t>
+          <t>-0,69; 1,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,46</t>
+          <t>-0,75; 1,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,16</t>
+          <t>-1,14; 0,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,51</t>
+          <t>-1,0; 1,09</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,54</t>
+          <t>-0,03; 1,58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,66</t>
+          <t>-0,68; 0,71</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,94</t>
+          <t>-0,56; 0,96</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>102,64%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>25,24%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>22,39%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-12,05%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>102,64%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,8; 162,91</t>
+          <t>-3,35; 367,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,33; 95,4</t>
+          <t>-50,12; 174,23</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,85; 120,99</t>
+          <t>-48,13; 235,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,73; 356,11</t>
+          <t>-42,73; 151,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 164,31</t>
+          <t>-64,2; 101,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 224,82</t>
+          <t>-57,85; 137,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 162,62</t>
+          <t>-5,13; 173,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 71,91</t>
+          <t>-43,11; 81,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 101,59</t>
+          <t>-37,63; 104,3</t>
         </is>
       </c>
     </row>
